--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131117617</v>
+        <v>131136126</v>
       </c>
       <c r="B12" t="n">
         <v>91828</v>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620884</v>
+        <v>621004</v>
       </c>
       <c r="R12" t="n">
-        <v>6876450</v>
+        <v>6876453</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1735,6 +1735,224 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131117093</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57073</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>620943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6876466</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131117107</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80348</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620884</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6876450</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R4" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R5" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R4" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R5" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131116531</v>
       </c>
       <c r="B3" t="n">
-        <v>56456</v>
+        <v>56458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>131117093</v>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131116531</v>
       </c>
       <c r="B3" t="n">
-        <v>56458</v>
+        <v>56459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>131117093</v>
       </c>
       <c r="B13" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R4" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R5" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131117122</v>
+        <v>131117242</v>
       </c>
       <c r="B6" t="n">
         <v>80354</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621039</v>
+        <v>621021</v>
       </c>
       <c r="R6" t="n">
-        <v>6876437</v>
+        <v>6876450</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131117242</v>
+        <v>131117122</v>
       </c>
       <c r="B7" t="n">
         <v>80354</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621021</v>
+        <v>621039</v>
       </c>
       <c r="R7" t="n">
-        <v>6876450</v>
+        <v>6876437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131116531</v>
       </c>
       <c r="B3" t="n">
-        <v>56459</v>
+        <v>56460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131117242</v>
+        <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621021</v>
+        <v>621039</v>
       </c>
       <c r="R6" t="n">
-        <v>6876450</v>
+        <v>6876437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131117122</v>
+        <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621039</v>
+        <v>621021</v>
       </c>
       <c r="R7" t="n">
-        <v>6876437</v>
+        <v>6876450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131116531</v>
       </c>
       <c r="B3" t="n">
-        <v>56460</v>
+        <v>56463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131116436</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131117304</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>131117093</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131117228</v>
       </c>
       <c r="B2" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131116531</v>
       </c>
       <c r="B3" t="n">
-        <v>56463</v>
+        <v>56464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116436</v>
+        <v>131117304</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620927</v>
+        <v>621008</v>
       </c>
       <c r="R4" t="n">
-        <v>6876471</v>
+        <v>6876450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117304</v>
+        <v>131116436</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621008</v>
+        <v>620927</v>
       </c>
       <c r="R5" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>131117122</v>
       </c>
       <c r="B6" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131117242</v>
       </c>
       <c r="B7" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131117266</v>
       </c>
       <c r="B8" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>131117134</v>
       </c>
       <c r="B9" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>131117199</v>
       </c>
       <c r="B10" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131116498</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>131136126</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>131117093</v>
       </c>
       <c r="B13" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131117107</v>
       </c>
       <c r="B14" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,6 +1954,1564 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132518067</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57139</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>620884</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6876450</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132520555</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620991</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6876463</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132518000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57359</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>620870</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6876468</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132519214</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620896</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6876396</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132518954</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620862</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6876352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132518566</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>620837</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6876306</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132520399</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>621028</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6876450</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132520210</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80457</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620977</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6876427</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132520048</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>620968</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6876430</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132518386</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>620884</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6876450</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132519505</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>620931</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6876407</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132520156</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>620972</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6876429</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132520350</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>621045</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6876447</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132519758</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>620954</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6876430</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132520442</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91912</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>621020</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6876456</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132518532</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>620884</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6876450</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R19" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132518566</v>
+        <v>132518954</v>
       </c>
       <c r="B20" t="n">
-        <v>5495</v>
+        <v>57945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620837</v>
+        <v>620862</v>
       </c>
       <c r="R20" t="n">
-        <v>6876306</v>
+        <v>6876352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132520399</v>
+        <v>132518566</v>
       </c>
       <c r="B21" t="n">
-        <v>80422</v>
+        <v>5495</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>101410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621028</v>
+        <v>620837</v>
       </c>
       <c r="R21" t="n">
-        <v>6876450</v>
+        <v>6876306</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132520156</v>
+        <v>132520350</v>
       </c>
       <c r="B26" t="n">
         <v>80422</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620972</v>
+        <v>621045</v>
       </c>
       <c r="R26" t="n">
-        <v>6876429</v>
+        <v>6876447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,7 +3130,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132520350</v>
+        <v>132520156</v>
       </c>
       <c r="B27" t="n">
         <v>80422</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621045</v>
+        <v>620972</v>
       </c>
       <c r="R27" t="n">
-        <v>6876447</v>
+        <v>6876429</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132520399</v>
+        <v>132518954</v>
       </c>
       <c r="B19" t="n">
-        <v>80422</v>
+        <v>57945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621028</v>
+        <v>620862</v>
       </c>
       <c r="R19" t="n">
-        <v>6876450</v>
+        <v>6876352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R20" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132518566</v>
+        <v>132520210</v>
       </c>
       <c r="B21" t="n">
-        <v>5495</v>
+        <v>80457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101410</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620837</v>
+        <v>620977</v>
       </c>
       <c r="R21" t="n">
-        <v>6876306</v>
+        <v>6876427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132520210</v>
+        <v>132520048</v>
       </c>
       <c r="B22" t="n">
-        <v>80457</v>
+        <v>80422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620977</v>
+        <v>620968</v>
       </c>
       <c r="R22" t="n">
-        <v>6876427</v>
+        <v>6876430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132520048</v>
+        <v>132518386</v>
       </c>
       <c r="B23" t="n">
-        <v>80422</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,34 +2753,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620968</v>
+        <v>620884</v>
       </c>
       <c r="R23" t="n">
-        <v>6876430</v>
+        <v>6876450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,45 +2839,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132518386</v>
+        <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620884</v>
+        <v>620931</v>
       </c>
       <c r="R24" t="n">
-        <v>6876450</v>
+        <v>6876407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132519505</v>
+        <v>132520350</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>80422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620931</v>
+        <v>621045</v>
       </c>
       <c r="R25" t="n">
-        <v>6876407</v>
+        <v>6876447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132520350</v>
+        <v>132520156</v>
       </c>
       <c r="B26" t="n">
         <v>80422</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621045</v>
+        <v>620972</v>
       </c>
       <c r="R26" t="n">
-        <v>6876447</v>
+        <v>6876429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132520156</v>
+        <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>80422</v>
+        <v>91855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620972</v>
+        <v>620954</v>
       </c>
       <c r="R27" t="n">
-        <v>6876429</v>
+        <v>6876430</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,34 +3227,30 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132519758</v>
+        <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91855</v>
+        <v>91912</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3262,10 +3258,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620954</v>
+        <v>621020</v>
       </c>
       <c r="R28" t="n">
-        <v>6876430</v>
+        <v>6876456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3320,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132520442</v>
+        <v>132518532</v>
       </c>
       <c r="B29" t="n">
-        <v>91912</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,30 +3331,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621020</v>
+        <v>620884</v>
       </c>
       <c r="R29" t="n">
-        <v>6876456</v>
+        <v>6876450</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3417,45 +3417,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132518532</v>
+        <v>132518566</v>
       </c>
       <c r="B30" t="n">
-        <v>57945</v>
+        <v>5482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>101920</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620884</v>
+        <v>620837</v>
       </c>
       <c r="R30" t="n">
-        <v>6876450</v>
+        <v>6876306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3496,6 +3501,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>132518067</v>
       </c>
       <c r="B15" t="n">
-        <v>57139</v>
+        <v>57140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132520555</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>132518000</v>
       </c>
       <c r="B17" t="n">
-        <v>57359</v>
+        <v>57360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>132519214</v>
       </c>
       <c r="B18" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>80424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R19" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132520399</v>
+        <v>132518954</v>
       </c>
       <c r="B20" t="n">
-        <v>80422</v>
+        <v>57946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621028</v>
+        <v>620862</v>
       </c>
       <c r="R20" t="n">
-        <v>6876450</v>
+        <v>6876352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132520210</v>
+        <v>132520048</v>
       </c>
       <c r="B21" t="n">
-        <v>80457</v>
+        <v>80424</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620977</v>
+        <v>620968</v>
       </c>
       <c r="R21" t="n">
-        <v>6876427</v>
+        <v>6876430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132520048</v>
+        <v>132520210</v>
       </c>
       <c r="B22" t="n">
-        <v>80422</v>
+        <v>80459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620968</v>
+        <v>620977</v>
       </c>
       <c r="R22" t="n">
-        <v>6876430</v>
+        <v>6876427</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
         <v>132518386</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>132520350</v>
       </c>
       <c r="B25" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>132520156</v>
       </c>
       <c r="B26" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132518532</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>132518067</v>
       </c>
       <c r="B15" t="n">
-        <v>57140</v>
+        <v>57144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132520555</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,50 +2155,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132518000</v>
+        <v>132519214</v>
       </c>
       <c r="B17" t="n">
-        <v>57360</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620870</v>
+        <v>620896</v>
       </c>
       <c r="R17" t="n">
-        <v>6876468</v>
+        <v>6876396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,45 +2252,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519214</v>
+        <v>132518000</v>
       </c>
       <c r="B18" t="n">
-        <v>58110</v>
+        <v>57364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620896</v>
+        <v>620870</v>
       </c>
       <c r="R18" t="n">
-        <v>6876396</v>
+        <v>6876468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
         <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>132518954</v>
       </c>
       <c r="B20" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>132520048</v>
       </c>
       <c r="B21" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>132520210</v>
       </c>
       <c r="B22" t="n">
-        <v>80459</v>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>132518386</v>
       </c>
       <c r="B23" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>132520350</v>
       </c>
       <c r="B25" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>132520156</v>
       </c>
       <c r="B26" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132518532</v>
       </c>
       <c r="B29" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2155,45 +2155,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519214</v>
+        <v>132518000</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>57364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620896</v>
+        <v>620870</v>
       </c>
       <c r="R17" t="n">
-        <v>6876396</v>
+        <v>6876468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,50 +2257,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132518000</v>
+        <v>132519214</v>
       </c>
       <c r="B18" t="n">
-        <v>57364</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620870</v>
+        <v>620896</v>
       </c>
       <c r="R18" t="n">
-        <v>6876468</v>
+        <v>6876396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2155,50 +2155,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132518000</v>
+        <v>132519214</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620870</v>
+        <v>620896</v>
       </c>
       <c r="R17" t="n">
-        <v>6876468</v>
+        <v>6876396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,45 +2252,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519214</v>
+        <v>132518000</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>57364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620896</v>
+        <v>620870</v>
       </c>
       <c r="R18" t="n">
-        <v>6876396</v>
+        <v>6876468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2155,45 +2155,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519214</v>
+        <v>132518000</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>57364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620896</v>
+        <v>620870</v>
       </c>
       <c r="R17" t="n">
-        <v>6876396</v>
+        <v>6876468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,50 +2257,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132518000</v>
+        <v>132519214</v>
       </c>
       <c r="B18" t="n">
-        <v>57364</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620870</v>
+        <v>620896</v>
       </c>
       <c r="R18" t="n">
-        <v>6876468</v>
+        <v>6876396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>132518067</v>
       </c>
       <c r="B15" t="n">
-        <v>57144</v>
+        <v>57145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132520555</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>132518000</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>57365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>132519214</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132520399</v>
+        <v>132518954</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>57951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621028</v>
+        <v>620862</v>
       </c>
       <c r="R19" t="n">
-        <v>6876450</v>
+        <v>6876352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R20" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,7 +2551,7 @@
         <v>132520048</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>132520210</v>
       </c>
       <c r="B22" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>132518386</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>132520350</v>
       </c>
       <c r="B25" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>132520156</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132518532</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>57951</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R19" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132520399</v>
+        <v>132518954</v>
       </c>
       <c r="B20" t="n">
-        <v>80433</v>
+        <v>57951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621028</v>
+        <v>620862</v>
       </c>
       <c r="R20" t="n">
-        <v>6876450</v>
+        <v>6876352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>132520048</v>
       </c>
       <c r="B21" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>132520210</v>
       </c>
       <c r="B22" t="n">
-        <v>80468</v>
+        <v>80469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>132518386</v>
       </c>
       <c r="B23" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>132519505</v>
       </c>
       <c r="B24" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>132520350</v>
       </c>
       <c r="B25" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>132520156</v>
       </c>
       <c r="B26" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>132519758</v>
       </c>
       <c r="B27" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>132520442</v>
       </c>
       <c r="B28" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131117228</v>
+        <v>132519922</v>
       </c>
       <c r="B2" t="n">
-        <v>80359</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621040</v>
+        <v>620965</v>
       </c>
       <c r="R2" t="n">
-        <v>6876449</v>
+        <v>6876430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131116531</v>
+        <v>131117075</v>
       </c>
       <c r="B3" t="n">
-        <v>56464</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620966</v>
+        <v>620999</v>
       </c>
       <c r="R3" t="n">
-        <v>6876458</v>
+        <v>6876414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131117304</v>
+        <v>132519758</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621008</v>
+        <v>620954</v>
       </c>
       <c r="R4" t="n">
-        <v>6876450</v>
+        <v>6876430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131116436</v>
+        <v>131116498</v>
       </c>
       <c r="B5" t="n">
-        <v>57889</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620927</v>
+        <v>620966</v>
       </c>
       <c r="R5" t="n">
-        <v>6876471</v>
+        <v>6876458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131117122</v>
+        <v>131116896</v>
       </c>
       <c r="B6" t="n">
-        <v>80359</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621039</v>
+        <v>620999</v>
       </c>
       <c r="R6" t="n">
-        <v>6876437</v>
+        <v>6876414</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,42 +1160,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131117242</v>
+        <v>132518386</v>
       </c>
       <c r="B7" t="n">
-        <v>80359</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621021</v>
+        <v>620884</v>
       </c>
       <c r="R7" t="n">
         <v>6876450</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131117266</v>
+        <v>131116675</v>
       </c>
       <c r="B8" t="n">
-        <v>80359</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621023</v>
+        <v>620994</v>
       </c>
       <c r="R8" t="n">
-        <v>6876463</v>
+        <v>6876416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131117134</v>
+        <v>131117107</v>
       </c>
       <c r="B9" t="n">
-        <v>80359</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,16 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621030</v>
+        <v>620884</v>
       </c>
       <c r="R9" t="n">
-        <v>6876442</v>
+        <v>6876450</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1433,6 +1436,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1451,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131117199</v>
+        <v>131117122</v>
       </c>
       <c r="B10" t="n">
-        <v>80359</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621032</v>
+        <v>621039</v>
       </c>
       <c r="R10" t="n">
-        <v>6876453</v>
+        <v>6876437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131116498</v>
+        <v>131117134</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620966</v>
+        <v>621030</v>
       </c>
       <c r="R11" t="n">
-        <v>6876458</v>
+        <v>6876442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131136126</v>
+        <v>131117199</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,19 +1660,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,7 +1684,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621004</v>
+        <v>621032</v>
       </c>
       <c r="R12" t="n">
         <v>6876453</v>
@@ -1706,12 +1714,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1738,65 +1746,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131117093</v>
+        <v>131117228</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620943</v>
+        <v>621040</v>
       </c>
       <c r="R13" t="n">
-        <v>6876466</v>
+        <v>6876449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1843,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131117107</v>
+        <v>131117242</v>
       </c>
       <c r="B14" t="n">
-        <v>80365</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1884,16 +1872,13 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620884</v>
+        <v>621021</v>
       </c>
       <c r="R14" t="n">
         <v>6876450</v>
@@ -1937,7 +1922,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1956,50 +1940,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132518067</v>
+        <v>131117255</v>
       </c>
       <c r="B15" t="n">
-        <v>57148</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620884</v>
+        <v>621023</v>
       </c>
       <c r="R15" t="n">
-        <v>6876450</v>
+        <v>6876463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2026,12 +2005,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132520555</v>
+        <v>132520048</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,34 +2048,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620991</v>
+        <v>620968</v>
       </c>
       <c r="R16" t="n">
-        <v>6876463</v>
+        <v>6876430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,50 +2134,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132518000</v>
+        <v>132520156</v>
       </c>
       <c r="B17" t="n">
-        <v>57369</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102954</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620870</v>
+        <v>620972</v>
       </c>
       <c r="R17" t="n">
-        <v>6876468</v>
+        <v>6876429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519214</v>
+        <v>132520350</v>
       </c>
       <c r="B18" t="n">
-        <v>58119</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2292,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620896</v>
+        <v>621045</v>
       </c>
       <c r="R18" t="n">
-        <v>6876396</v>
+        <v>6876447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132518954</v>
+        <v>132520399</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620862</v>
+        <v>621028</v>
       </c>
       <c r="R19" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,32 +2425,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132520399</v>
+        <v>132520210</v>
       </c>
       <c r="B20" t="n">
-        <v>80438</v>
+        <v>80499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621028</v>
+        <v>620977</v>
       </c>
       <c r="R20" t="n">
-        <v>6876450</v>
+        <v>6876427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,32 +2522,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132520048</v>
+        <v>131116436</v>
       </c>
       <c r="B21" t="n">
-        <v>80438</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620968</v>
+        <v>620927</v>
       </c>
       <c r="R21" t="n">
-        <v>6876430</v>
+        <v>6876471</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2613,12 +2587,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2619,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132520210</v>
+        <v>132518532</v>
       </c>
       <c r="B22" t="n">
-        <v>80473</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2630,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620977</v>
+        <v>620884</v>
       </c>
       <c r="R22" t="n">
-        <v>6876427</v>
+        <v>6876450</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,45 +2716,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132518386</v>
+        <v>132518954</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620884</v>
+        <v>620862</v>
       </c>
       <c r="R23" t="n">
-        <v>6876450</v>
+        <v>6876352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,45 +2813,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132519505</v>
+        <v>132520555</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620931</v>
+        <v>620991</v>
       </c>
       <c r="R24" t="n">
-        <v>6876407</v>
+        <v>6876463</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132520350</v>
+        <v>131117304</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621045</v>
+        <v>621008</v>
       </c>
       <c r="R25" t="n">
-        <v>6876447</v>
+        <v>6876450</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3001,12 +2975,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3033,45 +3007,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132520156</v>
+        <v>131117093</v>
       </c>
       <c r="B26" t="n">
-        <v>80438</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620972</v>
+        <v>620943</v>
       </c>
       <c r="R26" t="n">
-        <v>6876429</v>
+        <v>6876466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3098,12 +3092,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3130,45 +3124,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132519758</v>
+        <v>132518566</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>5484</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>101920</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620954</v>
+        <v>620837</v>
       </c>
       <c r="R27" t="n">
-        <v>6876430</v>
+        <v>6876306</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3209,6 +3208,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3227,41 +3227,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132520442</v>
+        <v>132518067</v>
       </c>
       <c r="B28" t="n">
-        <v>91938</v>
+        <v>57165</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621020</v>
+        <v>620884</v>
       </c>
       <c r="R28" t="n">
-        <v>6876456</v>
+        <v>6876450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3320,27 +3329,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132518532</v>
+        <v>132520291</v>
       </c>
       <c r="B29" t="n">
-        <v>57955</v>
+        <v>57165</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3348,17 +3357,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620884</v>
+        <v>621111</v>
       </c>
       <c r="R29" t="n">
-        <v>6876450</v>
+        <v>6876464</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3417,53 +3445,64 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132518566</v>
+        <v>132736947</v>
       </c>
       <c r="B30" t="n">
-        <v>5482</v>
+        <v>57816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101920</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620837</v>
+        <v>620999</v>
       </c>
       <c r="R30" t="n">
-        <v>6876306</v>
+        <v>6876426</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3487,12 +3526,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hanen överlämnade byte.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3501,22 +3555,414 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132518000</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>620870</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6876468</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132519214</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>620896</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6876396</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131116531</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>620966</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6876458</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132519505</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>620931</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6876407</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116896</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518386</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117107</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117122</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117134</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117199</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117228</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117255</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520048</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520156</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520350</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520399</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520210</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116436</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518532</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518954</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2907,6 +3022,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520555</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3004,6 +3124,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117304</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117093</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518566</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3326,6 +3461,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518067</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3442,6 +3582,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520291</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3570,6 +3715,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132736947</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3672,6 +3822,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132518000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3769,6 +3924,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519214</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3866,6 +4026,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116531</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3963,8 +4128,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>